--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -970,32 +970,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128899991</v>
+        <v>128899995</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595169</v>
+        <v>594969</v>
       </c>
       <c r="R5" t="n">
-        <v>6984812</v>
+        <v>6984740</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899995</v>
+        <v>128899991</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594969</v>
+        <v>595169</v>
       </c>
       <c r="R6" t="n">
-        <v>6984740</v>
+        <v>6984812</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1843,32 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128899988</v>
+        <v>128899996</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595444</v>
+        <v>594957</v>
       </c>
       <c r="R14" t="n">
-        <v>6984780</v>
+        <v>6984747</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,32 +1940,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128899996</v>
+        <v>128899988</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594957</v>
+        <v>595444</v>
       </c>
       <c r="R15" t="n">
-        <v>6984747</v>
+        <v>6984780</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -970,32 +970,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128899995</v>
+        <v>128899991</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594969</v>
+        <v>595169</v>
       </c>
       <c r="R5" t="n">
-        <v>6984740</v>
+        <v>6984812</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899991</v>
+        <v>128899995</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595169</v>
+        <v>594969</v>
       </c>
       <c r="R6" t="n">
-        <v>6984812</v>
+        <v>6984740</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899989</v>
+        <v>128899987</v>
       </c>
       <c r="B7" t="n">
-        <v>80225</v>
+        <v>82979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595356</v>
+        <v>595448</v>
       </c>
       <c r="R7" t="n">
-        <v>6984869</v>
+        <v>6984780</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899987</v>
+        <v>128899989</v>
       </c>
       <c r="B8" t="n">
-        <v>82979</v>
+        <v>80225</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,21 +1272,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595448</v>
+        <v>595356</v>
       </c>
       <c r="R8" t="n">
-        <v>6984780</v>
+        <v>6984869</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,32 +1455,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899981</v>
+        <v>128899982</v>
       </c>
       <c r="B10" t="n">
-        <v>98632</v>
+        <v>92806</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595265</v>
+        <v>595343</v>
       </c>
       <c r="R10" t="n">
-        <v>6984895</v>
+        <v>6984890</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,32 +1552,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899982</v>
+        <v>128899981</v>
       </c>
       <c r="B11" t="n">
-        <v>92806</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595343</v>
+        <v>595265</v>
       </c>
       <c r="R11" t="n">
-        <v>6984890</v>
+        <v>6984895</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899980</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899994</v>
       </c>
       <c r="B3" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128899990</v>
       </c>
       <c r="B4" t="n">
-        <v>96751</v>
+        <v>96755</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>128899991</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>128899995</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899987</v>
+        <v>128899989</v>
       </c>
       <c r="B7" t="n">
-        <v>82979</v>
+        <v>80229</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595448</v>
+        <v>595356</v>
       </c>
       <c r="R7" t="n">
-        <v>6984780</v>
+        <v>6984869</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899989</v>
+        <v>128899987</v>
       </c>
       <c r="B8" t="n">
-        <v>80225</v>
+        <v>82983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,21 +1272,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595356</v>
+        <v>595448</v>
       </c>
       <c r="R8" t="n">
-        <v>6984869</v>
+        <v>6984780</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,7 +1361,7 @@
         <v>128899992</v>
       </c>
       <c r="B9" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128899982</v>
       </c>
       <c r="B10" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128899981</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128899986</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128899985</v>
       </c>
       <c r="B13" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>128899996</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128899988</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -1164,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899989</v>
+        <v>128899987</v>
       </c>
       <c r="B7" t="n">
-        <v>80229</v>
+        <v>82983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595356</v>
+        <v>595448</v>
       </c>
       <c r="R7" t="n">
-        <v>6984869</v>
+        <v>6984780</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899987</v>
+        <v>128899989</v>
       </c>
       <c r="B8" t="n">
-        <v>82983</v>
+        <v>80229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,21 +1272,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595448</v>
+        <v>595356</v>
       </c>
       <c r="R8" t="n">
-        <v>6984780</v>
+        <v>6984869</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -1164,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899987</v>
+        <v>128899989</v>
       </c>
       <c r="B7" t="n">
-        <v>82983</v>
+        <v>80229</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595448</v>
+        <v>595356</v>
       </c>
       <c r="R7" t="n">
-        <v>6984780</v>
+        <v>6984869</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899989</v>
+        <v>128899987</v>
       </c>
       <c r="B8" t="n">
-        <v>80229</v>
+        <v>82983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,21 +1272,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595356</v>
+        <v>595448</v>
       </c>
       <c r="R8" t="n">
-        <v>6984869</v>
+        <v>6984780</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,32 +1455,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899982</v>
+        <v>128899981</v>
       </c>
       <c r="B10" t="n">
-        <v>92810</v>
+        <v>98636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595343</v>
+        <v>595265</v>
       </c>
       <c r="R10" t="n">
-        <v>6984890</v>
+        <v>6984895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,32 +1552,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899981</v>
+        <v>128899982</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>92810</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595265</v>
+        <v>595343</v>
       </c>
       <c r="R11" t="n">
-        <v>6984895</v>
+        <v>6984890</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899980</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899994</v>
       </c>
       <c r="B3" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128899990</v>
       </c>
       <c r="B4" t="n">
-        <v>96755</v>
+        <v>96762</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>128899991</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>128899995</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128899989</v>
       </c>
       <c r="B7" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>128899987</v>
       </c>
       <c r="B8" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>128899992</v>
       </c>
       <c r="B9" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,32 +1455,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899981</v>
+        <v>128899982</v>
       </c>
       <c r="B10" t="n">
-        <v>98636</v>
+        <v>92815</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595265</v>
+        <v>595343</v>
       </c>
       <c r="R10" t="n">
-        <v>6984895</v>
+        <v>6984890</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,32 +1552,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899982</v>
+        <v>128899981</v>
       </c>
       <c r="B11" t="n">
-        <v>92810</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595343</v>
+        <v>595265</v>
       </c>
       <c r="R11" t="n">
-        <v>6984890</v>
+        <v>6984895</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
         <v>128899986</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128899985</v>
       </c>
       <c r="B13" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>128899996</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128899988</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -869,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899991</v>
+        <v>128899990</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>96770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595169</v>
+        <v>595274</v>
       </c>
       <c r="R4" t="n">
-        <v>6984812</v>
+        <v>6984855</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128899990</v>
+        <v>128899991</v>
       </c>
       <c r="B5" t="n">
-        <v>96770</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595274</v>
+        <v>595169</v>
       </c>
       <c r="R5" t="n">
-        <v>6984855</v>
+        <v>6984812</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899980</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128899990</v>
       </c>
       <c r="B4" t="n">
-        <v>96770</v>
+        <v>96775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>128899995</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128899982</v>
       </c>
       <c r="B10" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128899981</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128899986</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128899985</v>
       </c>
       <c r="B13" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128899988</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899980</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899994</v>
       </c>
       <c r="B3" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,49 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899990</v>
+        <v>128899991</v>
       </c>
       <c r="B4" t="n">
-        <v>96775</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595274</v>
+        <v>595169</v>
       </c>
       <c r="R4" t="n">
-        <v>6984855</v>
+        <v>6984812</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128899991</v>
+        <v>128899995</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595169</v>
+        <v>594969</v>
       </c>
       <c r="R5" t="n">
-        <v>6984812</v>
+        <v>6984740</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,45 +1063,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899995</v>
+        <v>128899990</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>96778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594969</v>
+        <v>595274</v>
       </c>
       <c r="R6" t="n">
-        <v>6984740</v>
+        <v>6984855</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,7 +1167,7 @@
         <v>128899987</v>
       </c>
       <c r="B7" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>128899989</v>
       </c>
       <c r="B8" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>128899992</v>
       </c>
       <c r="B9" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128899982</v>
       </c>
       <c r="B10" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128899981</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128899986</v>
       </c>
       <c r="B12" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128899985</v>
       </c>
       <c r="B13" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>128899996</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128899988</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899991</v>
+        <v>128899995</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595169</v>
+        <v>594969</v>
       </c>
       <c r="R4" t="n">
-        <v>6984812</v>
+        <v>6984740</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,45 +966,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128899995</v>
+        <v>128899990</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>96778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594969</v>
+        <v>595274</v>
       </c>
       <c r="R5" t="n">
-        <v>6984740</v>
+        <v>6984855</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,49 +1067,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899990</v>
+        <v>128899991</v>
       </c>
       <c r="B6" t="n">
-        <v>96778</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595274</v>
+        <v>595169</v>
       </c>
       <c r="R6" t="n">
-        <v>6984855</v>
+        <v>6984812</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1843,32 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128899996</v>
+        <v>128899988</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594957</v>
+        <v>595444</v>
       </c>
       <c r="R14" t="n">
-        <v>6984747</v>
+        <v>6984780</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,32 +1940,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128899988</v>
+        <v>128899996</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595444</v>
+        <v>594957</v>
       </c>
       <c r="R15" t="n">
-        <v>6984780</v>
+        <v>6984747</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -1843,32 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128899988</v>
+        <v>128899996</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595444</v>
+        <v>594957</v>
       </c>
       <c r="R14" t="n">
-        <v>6984780</v>
+        <v>6984747</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,32 +1940,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128899996</v>
+        <v>128899988</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594957</v>
+        <v>595444</v>
       </c>
       <c r="R15" t="n">
-        <v>6984747</v>
+        <v>6984780</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -1164,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899987</v>
+        <v>128899989</v>
       </c>
       <c r="B7" t="n">
-        <v>82898</v>
+        <v>80140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595448</v>
+        <v>595356</v>
       </c>
       <c r="R7" t="n">
-        <v>6984780</v>
+        <v>6984869</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899989</v>
+        <v>128899987</v>
       </c>
       <c r="B8" t="n">
-        <v>80140</v>
+        <v>82898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,21 +1272,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595356</v>
+        <v>595448</v>
       </c>
       <c r="R8" t="n">
-        <v>6984869</v>
+        <v>6984780</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899980</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899994</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899995</v>
+        <v>128899991</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594969</v>
+        <v>595169</v>
       </c>
       <c r="R4" t="n">
-        <v>6984740</v>
+        <v>6984812</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,49 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128899990</v>
+        <v>128899995</v>
       </c>
       <c r="B5" t="n">
-        <v>96778</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595274</v>
+        <v>594969</v>
       </c>
       <c r="R5" t="n">
-        <v>6984855</v>
+        <v>6984740</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,45 +1063,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899991</v>
+        <v>128899990</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>96788</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595169</v>
+        <v>595274</v>
       </c>
       <c r="R6" t="n">
-        <v>6984812</v>
+        <v>6984855</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899989</v>
+        <v>128899987</v>
       </c>
       <c r="B7" t="n">
-        <v>80140</v>
+        <v>82902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595356</v>
+        <v>595448</v>
       </c>
       <c r="R7" t="n">
-        <v>6984869</v>
+        <v>6984780</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899987</v>
+        <v>128899989</v>
       </c>
       <c r="B8" t="n">
-        <v>82898</v>
+        <v>80144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,21 +1272,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595448</v>
+        <v>595356</v>
       </c>
       <c r="R8" t="n">
-        <v>6984780</v>
+        <v>6984869</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,7 +1361,7 @@
         <v>128899992</v>
       </c>
       <c r="B9" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128899982</v>
       </c>
       <c r="B10" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128899981</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128899986</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128899985</v>
       </c>
       <c r="B13" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>128899996</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128899988</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -1843,32 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128899996</v>
+        <v>128899988</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594957</v>
+        <v>595444</v>
       </c>
       <c r="R14" t="n">
-        <v>6984747</v>
+        <v>6984780</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,32 +1940,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128899988</v>
+        <v>128899996</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595444</v>
+        <v>594957</v>
       </c>
       <c r="R15" t="n">
-        <v>6984780</v>
+        <v>6984747</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899980</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -966,45 +966,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128899995</v>
+        <v>128899990</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>96795</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594969</v>
+        <v>595274</v>
       </c>
       <c r="R5" t="n">
-        <v>6984740</v>
+        <v>6984855</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,49 +1067,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899990</v>
+        <v>128899995</v>
       </c>
       <c r="B6" t="n">
-        <v>96788</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595274</v>
+        <v>594969</v>
       </c>
       <c r="R6" t="n">
-        <v>6984855</v>
+        <v>6984740</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899987</v>
+        <v>128899989</v>
       </c>
       <c r="B7" t="n">
-        <v>82902</v>
+        <v>80144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595448</v>
+        <v>595356</v>
       </c>
       <c r="R7" t="n">
-        <v>6984780</v>
+        <v>6984869</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899989</v>
+        <v>128899987</v>
       </c>
       <c r="B8" t="n">
-        <v>80144</v>
+        <v>82871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,21 +1272,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595356</v>
+        <v>595448</v>
       </c>
       <c r="R8" t="n">
-        <v>6984869</v>
+        <v>6984780</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,7 +1361,7 @@
         <v>128899992</v>
       </c>
       <c r="B9" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128899982</v>
       </c>
       <c r="B10" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128899981</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128899986</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128899985</v>
       </c>
       <c r="B13" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,32 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128899988</v>
+        <v>128899996</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595444</v>
+        <v>594957</v>
       </c>
       <c r="R14" t="n">
-        <v>6984780</v>
+        <v>6984747</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,32 +1940,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128899996</v>
+        <v>128899988</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594957</v>
+        <v>595444</v>
       </c>
       <c r="R15" t="n">
-        <v>6984747</v>
+        <v>6984780</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899980</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899994</v>
       </c>
       <c r="B3" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899991</v>
+        <v>128899990</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>96797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595169</v>
+        <v>595274</v>
       </c>
       <c r="R4" t="n">
-        <v>6984812</v>
+        <v>6984855</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128899990</v>
+        <v>128899991</v>
       </c>
       <c r="B5" t="n">
-        <v>96795</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595274</v>
+        <v>595169</v>
       </c>
       <c r="R5" t="n">
-        <v>6984855</v>
+        <v>6984812</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,7 +1070,7 @@
         <v>128899995</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899989</v>
+        <v>128899987</v>
       </c>
       <c r="B7" t="n">
-        <v>80144</v>
+        <v>82873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595356</v>
+        <v>595448</v>
       </c>
       <c r="R7" t="n">
-        <v>6984869</v>
+        <v>6984780</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899987</v>
+        <v>128899989</v>
       </c>
       <c r="B8" t="n">
-        <v>82871</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,21 +1272,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595448</v>
+        <v>595356</v>
       </c>
       <c r="R8" t="n">
-        <v>6984780</v>
+        <v>6984869</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,7 +1361,7 @@
         <v>128899992</v>
       </c>
       <c r="B9" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,32 +1455,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899982</v>
+        <v>128899981</v>
       </c>
       <c r="B10" t="n">
-        <v>92845</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595343</v>
+        <v>595265</v>
       </c>
       <c r="R10" t="n">
-        <v>6984890</v>
+        <v>6984895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,32 +1552,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899981</v>
+        <v>128899982</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>92847</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595265</v>
+        <v>595343</v>
       </c>
       <c r="R11" t="n">
-        <v>6984895</v>
+        <v>6984890</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
         <v>128899986</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128899985</v>
       </c>
       <c r="B13" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>128899996</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128899988</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -869,49 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899990</v>
+        <v>128899995</v>
       </c>
       <c r="B4" t="n">
-        <v>96797</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595274</v>
+        <v>594969</v>
       </c>
       <c r="R4" t="n">
-        <v>6984855</v>
+        <v>6984740</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,45 +966,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128899991</v>
+        <v>128899990</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>96797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595169</v>
+        <v>595274</v>
       </c>
       <c r="R5" t="n">
-        <v>6984812</v>
+        <v>6984855</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899995</v>
+        <v>128899991</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594969</v>
+        <v>595169</v>
       </c>
       <c r="R6" t="n">
-        <v>6984740</v>
+        <v>6984812</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1843,32 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128899996</v>
+        <v>128899988</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594957</v>
+        <v>595444</v>
       </c>
       <c r="R14" t="n">
-        <v>6984747</v>
+        <v>6984780</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,32 +1940,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128899988</v>
+        <v>128899996</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595444</v>
+        <v>594957</v>
       </c>
       <c r="R15" t="n">
-        <v>6984780</v>
+        <v>6984747</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899995</v>
+        <v>128899991</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594969</v>
+        <v>595169</v>
       </c>
       <c r="R4" t="n">
-        <v>6984740</v>
+        <v>6984812</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,49 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128899990</v>
+        <v>128899995</v>
       </c>
       <c r="B5" t="n">
-        <v>96797</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595274</v>
+        <v>594969</v>
       </c>
       <c r="R5" t="n">
-        <v>6984855</v>
+        <v>6984740</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,45 +1063,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899991</v>
+        <v>128899990</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>96797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595169</v>
+        <v>595274</v>
       </c>
       <c r="R6" t="n">
-        <v>6984812</v>
+        <v>6984855</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899980</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -966,45 +966,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128899995</v>
+        <v>128899990</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>96823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594969</v>
+        <v>595274</v>
       </c>
       <c r="R5" t="n">
-        <v>6984740</v>
+        <v>6984855</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,49 +1067,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899990</v>
+        <v>128899995</v>
       </c>
       <c r="B6" t="n">
-        <v>96797</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595274</v>
+        <v>594969</v>
       </c>
       <c r="R6" t="n">
-        <v>6984855</v>
+        <v>6984740</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899987</v>
+        <v>128899989</v>
       </c>
       <c r="B7" t="n">
-        <v>82873</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595448</v>
+        <v>595356</v>
       </c>
       <c r="R7" t="n">
-        <v>6984780</v>
+        <v>6984869</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899989</v>
+        <v>128899987</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>82873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,21 +1272,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595356</v>
+        <v>595448</v>
       </c>
       <c r="R8" t="n">
-        <v>6984869</v>
+        <v>6984780</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,7 +1458,7 @@
         <v>128899981</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128899982</v>
       </c>
       <c r="B11" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128899986</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128899985</v>
       </c>
       <c r="B13" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>128899988</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899980</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -869,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899991</v>
+        <v>128899990</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>96824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595169</v>
+        <v>595274</v>
       </c>
       <c r="R4" t="n">
-        <v>6984812</v>
+        <v>6984855</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128899990</v>
+        <v>128899991</v>
       </c>
       <c r="B5" t="n">
-        <v>96823</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595274</v>
+        <v>595169</v>
       </c>
       <c r="R5" t="n">
-        <v>6984855</v>
+        <v>6984812</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,7 +1070,7 @@
         <v>128899995</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1455,32 +1455,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899981</v>
+        <v>128899982</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>92834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595265</v>
+        <v>595343</v>
       </c>
       <c r="R10" t="n">
-        <v>6984895</v>
+        <v>6984890</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,32 +1552,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899982</v>
+        <v>128899981</v>
       </c>
       <c r="B11" t="n">
-        <v>92833</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595343</v>
+        <v>595265</v>
       </c>
       <c r="R11" t="n">
-        <v>6984890</v>
+        <v>6984895</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
         <v>128899986</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128899985</v>
       </c>
       <c r="B13" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,32 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128899988</v>
+        <v>128899996</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595444</v>
+        <v>594957</v>
       </c>
       <c r="R14" t="n">
-        <v>6984780</v>
+        <v>6984747</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,32 +1940,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128899996</v>
+        <v>128899988</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594957</v>
+        <v>595444</v>
       </c>
       <c r="R15" t="n">
-        <v>6984747</v>
+        <v>6984780</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899980</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -869,49 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899990</v>
+        <v>128899995</v>
       </c>
       <c r="B4" t="n">
-        <v>96824</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595274</v>
+        <v>594969</v>
       </c>
       <c r="R4" t="n">
-        <v>6984855</v>
+        <v>6984740</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,45 +966,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128899991</v>
+        <v>128899990</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>96825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595169</v>
+        <v>595274</v>
       </c>
       <c r="R5" t="n">
-        <v>6984812</v>
+        <v>6984855</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899995</v>
+        <v>128899991</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594969</v>
+        <v>595169</v>
       </c>
       <c r="R6" t="n">
-        <v>6984740</v>
+        <v>6984812</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899989</v>
+        <v>128899987</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>82873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595356</v>
+        <v>595448</v>
       </c>
       <c r="R7" t="n">
-        <v>6984869</v>
+        <v>6984780</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899987</v>
+        <v>128899989</v>
       </c>
       <c r="B8" t="n">
-        <v>82873</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,21 +1272,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595448</v>
+        <v>595356</v>
       </c>
       <c r="R8" t="n">
-        <v>6984780</v>
+        <v>6984869</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,32 +1455,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899982</v>
+        <v>128899981</v>
       </c>
       <c r="B10" t="n">
-        <v>92834</v>
+        <v>98706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595343</v>
+        <v>595265</v>
       </c>
       <c r="R10" t="n">
-        <v>6984890</v>
+        <v>6984895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,32 +1552,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899981</v>
+        <v>128899982</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>92834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595265</v>
+        <v>595343</v>
       </c>
       <c r="R11" t="n">
-        <v>6984895</v>
+        <v>6984890</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
         <v>128899986</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128899988</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899980</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899994</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128899995</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128899990</v>
       </c>
       <c r="B5" t="n">
-        <v>96825</v>
+        <v>96829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>128899991</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128899987</v>
       </c>
       <c r="B7" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>128899989</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>128899992</v>
       </c>
       <c r="B9" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,32 +1455,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899981</v>
+        <v>128899982</v>
       </c>
       <c r="B10" t="n">
-        <v>98706</v>
+        <v>92837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595265</v>
+        <v>595343</v>
       </c>
       <c r="R10" t="n">
-        <v>6984895</v>
+        <v>6984890</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,32 +1552,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899982</v>
+        <v>128899981</v>
       </c>
       <c r="B11" t="n">
-        <v>92834</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595343</v>
+        <v>595265</v>
       </c>
       <c r="R11" t="n">
-        <v>6984890</v>
+        <v>6984895</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
         <v>128899986</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128899985</v>
       </c>
       <c r="B13" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>128899996</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128899988</v>
       </c>
       <c r="B15" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -869,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899995</v>
+        <v>128899990</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>96829</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594969</v>
+        <v>595274</v>
       </c>
       <c r="R4" t="n">
-        <v>6984740</v>
+        <v>6984855</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128899990</v>
+        <v>128899991</v>
       </c>
       <c r="B5" t="n">
-        <v>96829</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595274</v>
+        <v>595169</v>
       </c>
       <c r="R5" t="n">
-        <v>6984855</v>
+        <v>6984812</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899991</v>
+        <v>128899995</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595169</v>
+        <v>594969</v>
       </c>
       <c r="R6" t="n">
-        <v>6984812</v>
+        <v>6984740</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899980</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899994</v>
       </c>
       <c r="B3" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128899990</v>
       </c>
       <c r="B4" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>128899991</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>128899995</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128899987</v>
       </c>
       <c r="B7" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>128899989</v>
       </c>
       <c r="B8" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>128899992</v>
       </c>
       <c r="B9" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128899982</v>
       </c>
       <c r="B10" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128899981</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128899986</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128899985</v>
       </c>
       <c r="B13" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,32 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128899996</v>
+        <v>128899988</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594957</v>
+        <v>595444</v>
       </c>
       <c r="R14" t="n">
-        <v>6984747</v>
+        <v>6984780</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,32 +1940,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128899988</v>
+        <v>128899996</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595444</v>
+        <v>594957</v>
       </c>
       <c r="R15" t="n">
-        <v>6984780</v>
+        <v>6984747</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899980</v>
+        <v>128899987</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594988</v>
+        <v>595448</v>
       </c>
       <c r="R2" t="n">
-        <v>6984749</v>
+        <v>6984780</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899994</v>
+        <v>128899990</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594982</v>
+        <v>595274</v>
       </c>
       <c r="R3" t="n">
-        <v>6984745</v>
+        <v>6984855</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,49 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899990</v>
+        <v>128899982</v>
       </c>
       <c r="B4" t="n">
-        <v>96831</v>
+        <v>93209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Halsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595274</v>
+        <v>595343</v>
       </c>
       <c r="R4" t="n">
-        <v>6984855</v>
+        <v>6984890</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,32 +970,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128899991</v>
+        <v>128899985</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595169</v>
+        <v>595414</v>
       </c>
       <c r="R5" t="n">
-        <v>6984812</v>
+        <v>6984864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,10 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899995</v>
+        <v>128899991</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1078,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594969</v>
+        <v>595169</v>
       </c>
       <c r="R6" t="n">
-        <v>6984740</v>
+        <v>6984812</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,32 +1164,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899987</v>
+        <v>128899996</v>
       </c>
       <c r="B7" t="n">
-        <v>82878</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595448</v>
+        <v>594957</v>
       </c>
       <c r="R7" t="n">
-        <v>6984780</v>
+        <v>6984747</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899989</v>
+        <v>128899992</v>
       </c>
       <c r="B8" t="n">
-        <v>80149</v>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,21 +1272,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595356</v>
+        <v>595137</v>
       </c>
       <c r="R8" t="n">
-        <v>6984869</v>
+        <v>6984778</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,10 +1358,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128899992</v>
+        <v>128899989</v>
       </c>
       <c r="B9" t="n">
-        <v>83012</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595137</v>
+        <v>595356</v>
       </c>
       <c r="R9" t="n">
-        <v>6984778</v>
+        <v>6984869</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,32 +1455,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899982</v>
+        <v>128899994</v>
       </c>
       <c r="B10" t="n">
-        <v>92839</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595343</v>
+        <v>594982</v>
       </c>
       <c r="R10" t="n">
-        <v>6984890</v>
+        <v>6984745</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899981</v>
+        <v>128899980</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595265</v>
+        <v>594988</v>
       </c>
       <c r="R11" t="n">
-        <v>6984895</v>
+        <v>6984749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,10 +1649,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128899986</v>
+        <v>128899981</v>
       </c>
       <c r="B12" t="n">
-        <v>98712</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595447</v>
+        <v>595265</v>
       </c>
       <c r="R12" t="n">
-        <v>6984783</v>
+        <v>6984895</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,32 +1746,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128899985</v>
+        <v>128899986</v>
       </c>
       <c r="B13" t="n">
-        <v>92500</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595414</v>
+        <v>595447</v>
       </c>
       <c r="R13" t="n">
-        <v>6984864</v>
+        <v>6984783</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1846,7 +1846,7 @@
         <v>128899988</v>
       </c>
       <c r="B14" t="n">
-        <v>98712</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,32 +1940,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128899996</v>
+        <v>128899995</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594957</v>
+        <v>594969</v>
       </c>
       <c r="R15" t="n">
-        <v>6984747</v>
+        <v>6984740</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 24732-2025 artfynd.xlsx
+++ b/artfynd/A 24732-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899987</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899990</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899982</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899985</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899991</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899996</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899992</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899989</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899994</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899980</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899981</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899986</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899988</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2034,8 +2104,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899995</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>